--- a/templates/R80302書式/支給申請/05_事業所確認票(様式第13号)_研修名_企業名.xlsx
+++ b/templates/R80302書式/支給申請/05_事業所確認票(様式第13号)_研修名_企業名.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1BpI-orXolZb0ng1yaMRipc3BjlHfTOGt\アシスタントチーム\業務マニュアル\03_支給申請\00_顧客確認\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agri0001-my.sharepoint.com/personal/dxhr024_agri0001_onmicrosoft_com/Documents/デスクトップ/document_generator_new/templates/R80302書式/支給申請/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7531D534-C4F3-451A-9712-6F9EBF4003A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30D2EFB0-FED9-4B41-B4BA-090671A025B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="44040" yWindow="11220" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="様式第13号" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="39">
   <si>
     <t>事業所名</t>
     <rPh sb="0" eb="3">
@@ -137,6 +137,19 @@
   </si>
   <si>
     <t>10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>事 業 主：</t>
+    <rPh sb="0" eb="1">
+      <t>コト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ゴウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>シュ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -563,6 +576,25 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>様式第13号（第１面）（R7.4）</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウシキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゴウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>メン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>様式第13号（第２面）</t>
     <rPh sb="0" eb="2">
       <t>ヨウシキ</t>
@@ -628,102 +660,6 @@
     <rPh sb="47" eb="49">
       <t>ショルイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>事 業 主</t>
-    <rPh sb="0" eb="1">
-      <t>コト</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ゴウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>シュ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>名     称：</t>
-    <rPh sb="0" eb="1">
-      <t>ナ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>様式第13号（第１面）（R8.4）</t>
-    <rPh sb="0" eb="2">
-      <t>ヨウシキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ゴウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ダイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>メン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>●●●●</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>●</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>顧客企業本社の管轄</t>
-    <rPh sb="0" eb="4">
-      <t>コキャクキギョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ホンシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>カンカツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>顧客企業名を入力する</t>
-    <rPh sb="0" eb="5">
-      <t>コキャクキギョウメイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>顧客企業の本社住所を入力する</t>
-    <rPh sb="0" eb="2">
-      <t>コキャク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キギョウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ホンシャ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ジュウショ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>●●●●●●</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -731,7 +667,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -806,20 +742,6 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF00B050"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1274,7 +1196,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1347,296 +1269,233 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1948,144 +1807,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="3.6328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" style="2" customWidth="1"/>
-    <col min="4" max="16" width="3.453125" style="2" customWidth="1"/>
-    <col min="17" max="20" width="4.26953125" style="2" customWidth="1"/>
-    <col min="21" max="21" width="4.7265625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="2.08984375" style="2" customWidth="1"/>
+    <col min="1" max="2" width="3.59765625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="22.73046875" style="2" customWidth="1"/>
+    <col min="4" max="16" width="3.46484375" style="2" customWidth="1"/>
+    <col min="17" max="20" width="4.265625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="4.73046875" style="2" customWidth="1"/>
+    <col min="22" max="22" width="2.1328125" style="2" customWidth="1"/>
     <col min="23" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-    </row>
-    <row r="2" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+    </row>
+    <row r="2" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K3" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
+    <row r="3" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="99" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="99"/>
+      <c r="M3" s="99"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="98"/>
       <c r="Q3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="31" t="s">
-        <v>41</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="R3" s="24"/>
       <c r="S3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" s="24"/>
+      <c r="U3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="T3" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="54" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="54"/>
+    </row>
+    <row r="4" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="92"/>
+      <c r="C4" s="92"/>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="3"/>
       <c r="U5" s="4"/>
     </row>
-    <row r="6" spans="1:21" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="66" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
-      <c r="P6" s="67"/>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="67"/>
-      <c r="U6" s="67"/>
-    </row>
-    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
+    <row r="6" spans="1:21" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="77" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="78"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="78"/>
+      <c r="M6" s="78"/>
+      <c r="N6" s="78"/>
+      <c r="O6" s="78"/>
+      <c r="P6" s="78"/>
+      <c r="Q6" s="78"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="78"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
+    </row>
+    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
       <c r="L7" s="1"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-    </row>
-    <row r="8" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F8" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="27"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="77" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" s="77"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="77"/>
-      <c r="P8" s="77"/>
-      <c r="Q8" s="77"/>
-      <c r="R8" s="77"/>
-      <c r="S8" s="77"/>
-      <c r="T8" s="77"/>
-      <c r="U8" s="77"/>
-    </row>
-    <row r="9" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+    </row>
+    <row r="8" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="66"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="66"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="66"/>
+    </row>
+    <row r="9" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -2102,28 +1948,26 @@
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
     </row>
-    <row r="10" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
-      <c r="L10" s="78" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="78"/>
-      <c r="N10" s="78"/>
-      <c r="O10" s="78"/>
-      <c r="P10" s="78"/>
-      <c r="Q10" s="78"/>
-      <c r="R10" s="78"/>
-      <c r="S10" s="78"/>
-      <c r="T10" s="78"/>
-      <c r="U10" s="78"/>
-    </row>
-    <row r="11" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="67"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="67"/>
+    </row>
+    <row r="11" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -2133,28 +1977,26 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
     </row>
-    <row r="12" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H12" s="1"/>
       <c r="I12" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K12" s="1"/>
-      <c r="L12" s="79" t="s">
-        <v>41</v>
-      </c>
-      <c r="M12" s="79"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="79"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="79"/>
-      <c r="R12" s="79"/>
-      <c r="S12" s="79"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="68"/>
+      <c r="P12" s="68"/>
+      <c r="Q12" s="68"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="68"/>
       <c r="T12" s="21" t="s">
         <v>6</v>
       </c>
       <c r="U12" s="18"/>
     </row>
-    <row r="13" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -2168,101 +2010,91 @@
       <c r="T13" s="1"/>
       <c r="U13" s="3"/>
     </row>
-    <row r="14" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="68" t="s">
+    <row r="15" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="69"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="68" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="69"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="69"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="70"/>
+      <c r="B15" s="80"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="79" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="81"/>
       <c r="Q15" s="71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R15" s="72"/>
       <c r="S15" s="72"/>
       <c r="T15" s="72"/>
       <c r="U15" s="73"/>
     </row>
-    <row r="16" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="35"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="55" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="44" t="s">
+    <row r="16" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="83"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="I16" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="44" t="s">
+      <c r="I16" s="94"/>
+      <c r="J16" s="90"/>
+      <c r="K16" s="90"/>
+      <c r="L16" s="90"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="93"/>
+      <c r="O16" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="P16" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q16" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="R16" s="82"/>
-      <c r="S16" s="82"/>
-      <c r="T16" s="82"/>
-      <c r="U16" s="83"/>
-    </row>
-    <row r="17" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="57"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="50"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="84"/>
-      <c r="R17" s="85"/>
-      <c r="S17" s="85"/>
-      <c r="T17" s="85"/>
-      <c r="U17" s="86"/>
-    </row>
-    <row r="18" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="P16" s="87"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="36"/>
+    </row>
+    <row r="17" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="44"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="64"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="61"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="62"/>
+      <c r="O17" s="86"/>
+      <c r="P17" s="88"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="39"/>
+    </row>
+    <row r="18" spans="1:21" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -2285,7 +2117,7 @@
       <c r="T18" s="8"/>
       <c r="U18" s="9"/>
     </row>
-    <row r="19" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>5</v>
       </c>
@@ -2310,556 +2142,556 @@
       <c r="T19" s="8"/>
       <c r="U19" s="9"/>
     </row>
-    <row r="20" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="80" t="s">
+    <row r="20" spans="1:21" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="80"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80" t="s">
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="80"/>
-      <c r="L20" s="80"/>
-      <c r="M20" s="80"/>
-      <c r="N20" s="80"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="80"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="70"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="70"/>
       <c r="Q20" s="71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R20" s="72"/>
       <c r="S20" s="72"/>
       <c r="T20" s="72"/>
       <c r="U20" s="73"/>
     </row>
-    <row r="21" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="61" t="s">
+    <row r="21" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="55"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="44" t="s">
+      <c r="B21" s="83"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="34"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="35"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="44" t="s">
+      <c r="I21" s="94"/>
+      <c r="J21" s="90"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="90"/>
+      <c r="M21" s="90"/>
+      <c r="N21" s="93"/>
+      <c r="O21" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="87"/>
-      <c r="R21" s="88"/>
-      <c r="S21" s="88"/>
-      <c r="T21" s="88"/>
-      <c r="U21" s="89"/>
-    </row>
-    <row r="22" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="45"/>
-      <c r="P22" s="46"/>
-      <c r="Q22" s="90"/>
-      <c r="R22" s="91"/>
-      <c r="S22" s="91"/>
-      <c r="T22" s="91"/>
-      <c r="U22" s="92"/>
-    </row>
-    <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="74" t="s">
+      <c r="P21" s="87"/>
+      <c r="Q21" s="74"/>
+      <c r="R21" s="75"/>
+      <c r="S21" s="75"/>
+      <c r="T21" s="75"/>
+      <c r="U21" s="76"/>
+    </row>
+    <row r="22" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="40"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="89"/>
+      <c r="P22" s="91"/>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="54"/>
+      <c r="T22" s="54"/>
+      <c r="U22" s="55"/>
+    </row>
+    <row r="23" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="95"/>
+      <c r="F23" s="95"/>
+      <c r="G23" s="96"/>
       <c r="H23" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="I23" s="43"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
-      <c r="M23" s="41"/>
-      <c r="N23" s="42"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="95"/>
+      <c r="L23" s="95"/>
+      <c r="M23" s="95"/>
+      <c r="N23" s="96"/>
       <c r="O23" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="93"/>
-      <c r="R23" s="94"/>
-      <c r="S23" s="94"/>
-      <c r="T23" s="94"/>
-      <c r="U23" s="95"/>
-    </row>
-    <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="74"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="42"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="51"/>
+      <c r="S23" s="51"/>
+      <c r="T23" s="51"/>
+      <c r="U23" s="52"/>
+    </row>
+    <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="46"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="96"/>
       <c r="H24" s="49"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="41"/>
-      <c r="L24" s="41"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="42"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="95"/>
+      <c r="M24" s="95"/>
+      <c r="N24" s="96"/>
       <c r="O24" s="49"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="93"/>
-      <c r="R24" s="94"/>
-      <c r="S24" s="94"/>
-      <c r="T24" s="94"/>
-      <c r="U24" s="95"/>
-    </row>
-    <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="74" t="s">
+      <c r="P24" s="69"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="51"/>
+      <c r="S24" s="51"/>
+      <c r="T24" s="51"/>
+      <c r="U24" s="52"/>
+    </row>
+    <row r="25" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="40"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="96"/>
       <c r="H25" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="I25" s="43"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="42"/>
+      <c r="I25" s="97"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="96"/>
       <c r="O25" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="93"/>
-      <c r="R25" s="94"/>
-      <c r="S25" s="94"/>
-      <c r="T25" s="94"/>
-      <c r="U25" s="95"/>
-    </row>
-    <row r="26" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="74"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="75"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="42"/>
+      <c r="P25" s="69"/>
+      <c r="Q25" s="50"/>
+      <c r="R25" s="51"/>
+      <c r="S25" s="51"/>
+      <c r="T25" s="51"/>
+      <c r="U25" s="52"/>
+    </row>
+    <row r="26" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="46"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="95"/>
+      <c r="G26" s="96"/>
       <c r="H26" s="49"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="41"/>
-      <c r="L26" s="41"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="42"/>
+      <c r="I26" s="97"/>
+      <c r="J26" s="95"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="95"/>
+      <c r="M26" s="95"/>
+      <c r="N26" s="96"/>
       <c r="O26" s="49"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="93"/>
-      <c r="R26" s="94"/>
-      <c r="S26" s="94"/>
-      <c r="T26" s="94"/>
-      <c r="U26" s="95"/>
-    </row>
-    <row r="27" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="74" t="s">
+      <c r="P26" s="69"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="51"/>
+      <c r="S26" s="51"/>
+      <c r="T26" s="51"/>
+      <c r="U26" s="52"/>
+    </row>
+    <row r="27" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="75"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="42"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="96"/>
       <c r="H27" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="I27" s="43"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="41"/>
-      <c r="L27" s="41"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="42"/>
+      <c r="I27" s="97"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
+      <c r="M27" s="95"/>
+      <c r="N27" s="96"/>
       <c r="O27" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="93"/>
-      <c r="R27" s="94"/>
-      <c r="S27" s="94"/>
-      <c r="T27" s="94"/>
-      <c r="U27" s="95"/>
-    </row>
-    <row r="28" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="74"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="75"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="42"/>
+      <c r="P27" s="69"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="51"/>
+      <c r="S27" s="51"/>
+      <c r="T27" s="51"/>
+      <c r="U27" s="52"/>
+    </row>
+    <row r="28" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="46"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="95"/>
+      <c r="F28" s="95"/>
+      <c r="G28" s="96"/>
       <c r="H28" s="49"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="41"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="42"/>
+      <c r="I28" s="97"/>
+      <c r="J28" s="95"/>
+      <c r="K28" s="95"/>
+      <c r="L28" s="95"/>
+      <c r="M28" s="95"/>
+      <c r="N28" s="96"/>
       <c r="O28" s="49"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="93"/>
-      <c r="R28" s="94"/>
-      <c r="S28" s="94"/>
-      <c r="T28" s="94"/>
-      <c r="U28" s="95"/>
-    </row>
-    <row r="29" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="52" t="s">
+      <c r="P28" s="69"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="51"/>
+      <c r="S28" s="51"/>
+      <c r="T28" s="51"/>
+      <c r="U28" s="52"/>
+    </row>
+    <row r="29" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="56"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="45" t="s">
+      <c r="B29" s="42"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="I29" s="37"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="45" t="s">
+      <c r="I29" s="63"/>
+      <c r="J29" s="59"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="P29" s="46"/>
-      <c r="Q29" s="90"/>
-      <c r="R29" s="91"/>
-      <c r="S29" s="91"/>
-      <c r="T29" s="91"/>
-      <c r="U29" s="92"/>
-    </row>
-    <row r="30" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="53"/>
-      <c r="B30" s="57"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="60"/>
-      <c r="J30" s="58"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="58"/>
-      <c r="M30" s="58"/>
-      <c r="N30" s="59"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="96"/>
-      <c r="R30" s="97"/>
-      <c r="S30" s="97"/>
-      <c r="T30" s="97"/>
-      <c r="U30" s="98"/>
-    </row>
-    <row r="31" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="61" t="s">
+      <c r="P29" s="91"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="55"/>
+    </row>
+    <row r="30" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="41"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="86"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="61"/>
+      <c r="L30" s="61"/>
+      <c r="M30" s="61"/>
+      <c r="N30" s="62"/>
+      <c r="O30" s="86"/>
+      <c r="P30" s="88"/>
+      <c r="Q30" s="56"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="58"/>
+    </row>
+    <row r="31" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="55"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="44" t="s">
+      <c r="B31" s="83"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="90"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="I31" s="34"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="36"/>
-      <c r="O31" s="44" t="s">
+      <c r="I31" s="94"/>
+      <c r="J31" s="90"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="90"/>
+      <c r="M31" s="90"/>
+      <c r="N31" s="93"/>
+      <c r="O31" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="87"/>
-      <c r="R31" s="88"/>
-      <c r="S31" s="88"/>
-      <c r="T31" s="88"/>
-      <c r="U31" s="89"/>
-    </row>
-    <row r="32" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="52"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="38"/>
-      <c r="L32" s="38"/>
-      <c r="M32" s="38"/>
-      <c r="N32" s="39"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="46"/>
-      <c r="Q32" s="90"/>
-      <c r="R32" s="91"/>
-      <c r="S32" s="91"/>
-      <c r="T32" s="91"/>
-      <c r="U32" s="92"/>
-    </row>
-    <row r="33" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="74" t="s">
+      <c r="P31" s="87"/>
+      <c r="Q31" s="74"/>
+      <c r="R31" s="75"/>
+      <c r="S31" s="75"/>
+      <c r="T31" s="75"/>
+      <c r="U31" s="76"/>
+    </row>
+    <row r="32" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="40"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="59"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="59"/>
+      <c r="M32" s="59"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="89"/>
+      <c r="P32" s="91"/>
+      <c r="Q32" s="53"/>
+      <c r="R32" s="54"/>
+      <c r="S32" s="54"/>
+      <c r="T32" s="54"/>
+      <c r="U32" s="55"/>
+    </row>
+    <row r="33" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="75"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="42"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="95"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="96"/>
       <c r="H33" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="I33" s="43"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="42"/>
+      <c r="I33" s="97"/>
+      <c r="J33" s="95"/>
+      <c r="K33" s="95"/>
+      <c r="L33" s="95"/>
+      <c r="M33" s="95"/>
+      <c r="N33" s="96"/>
       <c r="O33" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="93"/>
-      <c r="R33" s="94"/>
-      <c r="S33" s="94"/>
-      <c r="T33" s="94"/>
-      <c r="U33" s="95"/>
-    </row>
-    <row r="34" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="74"/>
-      <c r="B34" s="40"/>
-      <c r="C34" s="75"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="42"/>
+      <c r="P33" s="69"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="51"/>
+      <c r="S33" s="51"/>
+      <c r="T33" s="51"/>
+      <c r="U33" s="52"/>
+    </row>
+    <row r="34" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="46"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="96"/>
       <c r="H34" s="49"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="42"/>
+      <c r="I34" s="97"/>
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="95"/>
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
       <c r="O34" s="49"/>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="93"/>
-      <c r="R34" s="94"/>
-      <c r="S34" s="94"/>
-      <c r="T34" s="94"/>
-      <c r="U34" s="95"/>
-    </row>
-    <row r="35" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="74" t="s">
+      <c r="P34" s="69"/>
+      <c r="Q34" s="50"/>
+      <c r="R34" s="51"/>
+      <c r="S34" s="51"/>
+      <c r="T34" s="51"/>
+      <c r="U34" s="52"/>
+    </row>
+    <row r="35" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="40"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="42"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="95"/>
+      <c r="F35" s="95"/>
+      <c r="G35" s="96"/>
       <c r="H35" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="I35" s="43"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="42"/>
+      <c r="I35" s="97"/>
+      <c r="J35" s="95"/>
+      <c r="K35" s="95"/>
+      <c r="L35" s="95"/>
+      <c r="M35" s="95"/>
+      <c r="N35" s="96"/>
       <c r="O35" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="93"/>
-      <c r="R35" s="94"/>
-      <c r="S35" s="94"/>
-      <c r="T35" s="94"/>
-      <c r="U35" s="95"/>
-    </row>
-    <row r="36" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="74"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="75"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="42"/>
+      <c r="P35" s="69"/>
+      <c r="Q35" s="50"/>
+      <c r="R35" s="51"/>
+      <c r="S35" s="51"/>
+      <c r="T35" s="51"/>
+      <c r="U35" s="52"/>
+    </row>
+    <row r="36" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="46"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="95"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="96"/>
       <c r="H36" s="49"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
-      <c r="M36" s="41"/>
-      <c r="N36" s="42"/>
+      <c r="I36" s="97"/>
+      <c r="J36" s="95"/>
+      <c r="K36" s="95"/>
+      <c r="L36" s="95"/>
+      <c r="M36" s="95"/>
+      <c r="N36" s="96"/>
       <c r="O36" s="49"/>
-      <c r="P36" s="48"/>
-      <c r="Q36" s="93"/>
-      <c r="R36" s="94"/>
-      <c r="S36" s="94"/>
-      <c r="T36" s="94"/>
-      <c r="U36" s="95"/>
-    </row>
-    <row r="37" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="74" t="s">
+      <c r="P36" s="69"/>
+      <c r="Q36" s="50"/>
+      <c r="R36" s="51"/>
+      <c r="S36" s="51"/>
+      <c r="T36" s="51"/>
+      <c r="U36" s="52"/>
+    </row>
+    <row r="37" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="40"/>
-      <c r="C37" s="75"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="42"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="96"/>
       <c r="H37" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="I37" s="43"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="41"/>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41"/>
-      <c r="N37" s="42"/>
+      <c r="I37" s="97"/>
+      <c r="J37" s="95"/>
+      <c r="K37" s="95"/>
+      <c r="L37" s="95"/>
+      <c r="M37" s="95"/>
+      <c r="N37" s="96"/>
       <c r="O37" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="P37" s="48"/>
-      <c r="Q37" s="93"/>
-      <c r="R37" s="94"/>
-      <c r="S37" s="94"/>
-      <c r="T37" s="94"/>
-      <c r="U37" s="95"/>
-    </row>
-    <row r="38" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="74"/>
-      <c r="B38" s="40"/>
-      <c r="C38" s="75"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="42"/>
+      <c r="P37" s="69"/>
+      <c r="Q37" s="50"/>
+      <c r="R37" s="51"/>
+      <c r="S37" s="51"/>
+      <c r="T37" s="51"/>
+      <c r="U37" s="52"/>
+    </row>
+    <row r="38" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="46"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="95"/>
+      <c r="F38" s="95"/>
+      <c r="G38" s="96"/>
       <c r="H38" s="49"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="42"/>
+      <c r="I38" s="97"/>
+      <c r="J38" s="95"/>
+      <c r="K38" s="95"/>
+      <c r="L38" s="95"/>
+      <c r="M38" s="95"/>
+      <c r="N38" s="96"/>
       <c r="O38" s="49"/>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="93"/>
-      <c r="R38" s="94"/>
-      <c r="S38" s="94"/>
-      <c r="T38" s="94"/>
-      <c r="U38" s="95"/>
-    </row>
-    <row r="39" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="52" t="s">
+      <c r="P38" s="69"/>
+      <c r="Q38" s="50"/>
+      <c r="R38" s="51"/>
+      <c r="S38" s="51"/>
+      <c r="T38" s="51"/>
+      <c r="U38" s="52"/>
+    </row>
+    <row r="39" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B39" s="56"/>
-      <c r="C39" s="63"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="45" t="s">
+      <c r="B39" s="42"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="I39" s="37"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="38"/>
-      <c r="M39" s="38"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="45" t="s">
+      <c r="I39" s="63"/>
+      <c r="J39" s="59"/>
+      <c r="K39" s="59"/>
+      <c r="L39" s="59"/>
+      <c r="M39" s="59"/>
+      <c r="N39" s="60"/>
+      <c r="O39" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="90"/>
-      <c r="R39" s="91"/>
-      <c r="S39" s="91"/>
-      <c r="T39" s="91"/>
-      <c r="U39" s="92"/>
-    </row>
-    <row r="40" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="53"/>
-      <c r="B40" s="57"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="57"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="60"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58"/>
-      <c r="M40" s="58"/>
-      <c r="N40" s="59"/>
-      <c r="O40" s="50"/>
-      <c r="P40" s="47"/>
-      <c r="Q40" s="96"/>
-      <c r="R40" s="97"/>
-      <c r="S40" s="97"/>
-      <c r="T40" s="97"/>
-      <c r="U40" s="98"/>
-    </row>
-    <row r="41" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P39" s="91"/>
+      <c r="Q39" s="53"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="54"/>
+      <c r="T39" s="54"/>
+      <c r="U39" s="55"/>
+    </row>
+    <row r="40" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="41"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="86"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="61"/>
+      <c r="K40" s="61"/>
+      <c r="L40" s="61"/>
+      <c r="M40" s="61"/>
+      <c r="N40" s="62"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="88"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="57"/>
+      <c r="S40" s="57"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="58"/>
+    </row>
+    <row r="41" spans="1:21" ht="4.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2882,7 +2714,7 @@
       <c r="T41" s="23"/>
       <c r="U41" s="23"/>
     </row>
-    <row r="42" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="10"/>
       <c r="B42" s="10"/>
       <c r="D42" s="7"/>
@@ -2890,47 +2722,45 @@
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
-      <c r="I42" s="99" t="s">
-        <v>19</v>
-      </c>
-      <c r="J42" s="100"/>
-      <c r="K42" s="100"/>
-      <c r="L42" s="100"/>
-      <c r="M42" s="100"/>
-      <c r="N42" s="100"/>
-      <c r="O42" s="100"/>
-      <c r="P42" s="101"/>
-      <c r="Q42" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="R42" s="82"/>
-      <c r="S42" s="82"/>
-      <c r="T42" s="82"/>
-      <c r="U42" s="83"/>
-    </row>
-    <row r="43" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I42" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="34"/>
+      <c r="R42" s="35"/>
+      <c r="S42" s="35"/>
+      <c r="T42" s="35"/>
+      <c r="U42" s="36"/>
+    </row>
+    <row r="43" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="10"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="102"/>
-      <c r="J43" s="103"/>
-      <c r="K43" s="103"/>
-      <c r="L43" s="103"/>
-      <c r="M43" s="103"/>
-      <c r="N43" s="103"/>
-      <c r="O43" s="103"/>
-      <c r="P43" s="104"/>
-      <c r="Q43" s="84"/>
-      <c r="R43" s="85"/>
-      <c r="S43" s="85"/>
-      <c r="T43" s="85"/>
-      <c r="U43" s="86"/>
-    </row>
-    <row r="44" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H43" s="26"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32"/>
+      <c r="N43" s="32"/>
+      <c r="O43" s="32"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="37"/>
+      <c r="R43" s="38"/>
+      <c r="S43" s="38"/>
+      <c r="T43" s="38"/>
+      <c r="U43" s="39"/>
+    </row>
+    <row r="44" spans="1:21" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="10"/>
       <c r="B44" s="10"/>
       <c r="D44" s="7"/>
@@ -2952,9 +2782,9 @@
       <c r="T44" s="12"/>
       <c r="U44" s="12"/>
     </row>
-    <row r="45" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B45" s="10"/>
       <c r="D45" s="7"/>
@@ -2976,9 +2806,9 @@
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
     </row>
-    <row r="46" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46" s="10"/>
       <c r="D46" s="7"/>
@@ -3000,12 +2830,12 @@
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
     </row>
-    <row r="47" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10"/>
       <c r="B48" s="10"/>
       <c r="D48" s="7"/>
@@ -3027,7 +2857,7 @@
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
     </row>
-    <row r="49" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10"/>
       <c r="B49" s="10"/>
       <c r="D49" s="7"/>
@@ -3049,74 +2879,74 @@
       <c r="T49" s="4"/>
       <c r="U49" s="4"/>
     </row>
-    <row r="50" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B50" s="15"/>
     </row>
-    <row r="51" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="14"/>
       <c r="B51" s="15"/>
     </row>
-    <row r="52" spans="1:21" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:21" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16"/>
       <c r="B52" s="15">
         <v>1</v>
       </c>
-      <c r="C52" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="65"/>
-      <c r="K52" s="65"/>
-      <c r="L52" s="65"/>
-      <c r="M52" s="65"/>
-      <c r="N52" s="65"/>
-      <c r="O52" s="65"/>
-      <c r="P52" s="65"/>
-      <c r="Q52" s="65"/>
-      <c r="R52" s="65"/>
-      <c r="S52" s="65"/>
-      <c r="T52" s="65"/>
-      <c r="U52" s="65"/>
-    </row>
-    <row r="53" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C52" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="27"/>
+      <c r="J52" s="27"/>
+      <c r="K52" s="27"/>
+      <c r="L52" s="27"/>
+      <c r="M52" s="27"/>
+      <c r="N52" s="27"/>
+      <c r="O52" s="27"/>
+      <c r="P52" s="27"/>
+      <c r="Q52" s="27"/>
+      <c r="R52" s="27"/>
+      <c r="S52" s="27"/>
+      <c r="T52" s="27"/>
+      <c r="U52" s="27"/>
+    </row>
+    <row r="53" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14"/>
       <c r="B53" s="15"/>
     </row>
-    <row r="54" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="15">
         <v>2</v>
       </c>
-      <c r="C54" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="65"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="65"/>
-      <c r="H54" s="65"/>
-      <c r="I54" s="65"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="65"/>
-      <c r="L54" s="65"/>
-      <c r="M54" s="65"/>
-      <c r="N54" s="65"/>
-      <c r="O54" s="65"/>
-      <c r="P54" s="65"/>
-      <c r="Q54" s="65"/>
-      <c r="R54" s="65"/>
-      <c r="S54" s="65"/>
-      <c r="T54" s="65"/>
-      <c r="U54" s="65"/>
-    </row>
-    <row r="55" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C54" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="27"/>
+      <c r="J54" s="27"/>
+      <c r="K54" s="27"/>
+      <c r="L54" s="27"/>
+      <c r="M54" s="27"/>
+      <c r="N54" s="27"/>
+      <c r="O54" s="27"/>
+      <c r="P54" s="27"/>
+      <c r="Q54" s="27"/>
+      <c r="R54" s="27"/>
+      <c r="S54" s="27"/>
+      <c r="T54" s="27"/>
+      <c r="U54" s="27"/>
+    </row>
+    <row r="55" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="15"/>
       <c r="C55" s="20"/>
       <c r="D55" s="20"/>
@@ -3138,63 +2968,63 @@
       <c r="T55" s="20"/>
       <c r="U55" s="20"/>
     </row>
-    <row r="56" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="15">
         <v>3</v>
       </c>
-      <c r="C56" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="D56" s="65"/>
-      <c r="E56" s="65"/>
-      <c r="F56" s="65"/>
-      <c r="G56" s="65"/>
-      <c r="H56" s="65"/>
-      <c r="I56" s="65"/>
-      <c r="J56" s="65"/>
-      <c r="K56" s="65"/>
-      <c r="L56" s="65"/>
-      <c r="M56" s="65"/>
-      <c r="N56" s="65"/>
-      <c r="O56" s="65"/>
-      <c r="P56" s="65"/>
-      <c r="Q56" s="65"/>
-      <c r="R56" s="65"/>
-      <c r="S56" s="65"/>
-      <c r="T56" s="65"/>
-      <c r="U56" s="65"/>
-    </row>
-    <row r="57" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C56" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="27"/>
+      <c r="K56" s="27"/>
+      <c r="L56" s="27"/>
+      <c r="M56" s="27"/>
+      <c r="N56" s="27"/>
+      <c r="O56" s="27"/>
+      <c r="P56" s="27"/>
+      <c r="Q56" s="27"/>
+      <c r="R56" s="27"/>
+      <c r="S56" s="27"/>
+      <c r="T56" s="27"/>
+      <c r="U56" s="27"/>
+    </row>
+    <row r="57" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
       <c r="B57" s="15"/>
     </row>
-    <row r="58" spans="1:21" ht="122.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="15">
         <v>4</v>
       </c>
-      <c r="C58" s="65" t="s">
-        <v>21</v>
-      </c>
-      <c r="D58" s="65"/>
-      <c r="E58" s="65"/>
-      <c r="F58" s="65"/>
-      <c r="G58" s="65"/>
-      <c r="H58" s="65"/>
-      <c r="I58" s="65"/>
-      <c r="J58" s="65"/>
-      <c r="K58" s="65"/>
-      <c r="L58" s="65"/>
-      <c r="M58" s="65"/>
-      <c r="N58" s="65"/>
-      <c r="O58" s="65"/>
-      <c r="P58" s="65"/>
-      <c r="Q58" s="65"/>
-      <c r="R58" s="65"/>
-      <c r="S58" s="65"/>
-      <c r="T58" s="65"/>
-      <c r="U58" s="65"/>
-    </row>
-    <row r="59" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C58" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
+      <c r="J58" s="27"/>
+      <c r="K58" s="27"/>
+      <c r="L58" s="27"/>
+      <c r="M58" s="27"/>
+      <c r="N58" s="27"/>
+      <c r="O58" s="27"/>
+      <c r="P58" s="27"/>
+      <c r="Q58" s="27"/>
+      <c r="R58" s="27"/>
+      <c r="S58" s="27"/>
+      <c r="T58" s="27"/>
+      <c r="U58" s="27"/>
+    </row>
+    <row r="59" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="15"/>
       <c r="C59" s="20"/>
       <c r="D59" s="20"/>
@@ -3216,57 +3046,108 @@
       <c r="T59" s="20"/>
       <c r="U59" s="20"/>
     </row>
-    <row r="60" spans="1:21" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="15">
         <v>5</v>
       </c>
-      <c r="C60" s="65" t="s">
-        <v>26</v>
-      </c>
-      <c r="D60" s="65"/>
-      <c r="E60" s="65"/>
-      <c r="F60" s="65"/>
-      <c r="G60" s="65"/>
-      <c r="H60" s="65"/>
-      <c r="I60" s="65"/>
-      <c r="J60" s="65"/>
-      <c r="K60" s="65"/>
-      <c r="L60" s="65"/>
-      <c r="M60" s="65"/>
-      <c r="N60" s="65"/>
-      <c r="O60" s="65"/>
-      <c r="P60" s="65"/>
-      <c r="Q60" s="65"/>
-      <c r="R60" s="65"/>
-      <c r="S60" s="65"/>
-      <c r="T60" s="65"/>
-      <c r="U60" s="65"/>
-    </row>
-    <row r="61" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C60" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="27"/>
+      <c r="I60" s="27"/>
+      <c r="J60" s="27"/>
+      <c r="K60" s="27"/>
+      <c r="L60" s="27"/>
+      <c r="M60" s="27"/>
+      <c r="N60" s="27"/>
+      <c r="O60" s="27"/>
+      <c r="P60" s="27"/>
+      <c r="Q60" s="27"/>
+      <c r="R60" s="27"/>
+      <c r="S60" s="27"/>
+      <c r="T60" s="27"/>
+      <c r="U60" s="27"/>
+    </row>
+    <row r="61" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="17"/>
       <c r="D61" s="17"/>
       <c r="E61" s="17"/>
       <c r="F61" s="17"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TnKGzpp7razOrBEJQcLu5l8g71BqahigqKKtgIMMboz9puKpCA+h1377OzrnTBLkLaYgNo3eFLe3WRjZ/LoyYQ==" saltValue="zjimMapVsSyQje17Pd++gg==" spinCount="100000" sheet="1"/>
   <mergeCells count="108">
-    <mergeCell ref="C56:U56"/>
-    <mergeCell ref="I42:P43"/>
-    <mergeCell ref="Q42:U43"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:C40"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:C36"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="Q35:U36"/>
-    <mergeCell ref="Q37:U38"/>
-    <mergeCell ref="Q39:U40"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="I39:N40"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="I31:N32"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="I33:N34"/>
+    <mergeCell ref="D35:G36"/>
+    <mergeCell ref="I35:N36"/>
+    <mergeCell ref="D37:G38"/>
+    <mergeCell ref="I37:N38"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="P33:P34"/>
+    <mergeCell ref="O27:O28"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="P39:P40"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D21:G22"/>
+    <mergeCell ref="I21:N22"/>
+    <mergeCell ref="D23:G24"/>
+    <mergeCell ref="I23:N24"/>
+    <mergeCell ref="D25:G26"/>
+    <mergeCell ref="I25:N26"/>
+    <mergeCell ref="D27:G28"/>
+    <mergeCell ref="I27:N28"/>
+    <mergeCell ref="D16:G17"/>
+    <mergeCell ref="I16:N17"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:C32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="I29:N30"/>
+    <mergeCell ref="D31:G32"/>
+    <mergeCell ref="B29:C30"/>
+    <mergeCell ref="C60:U60"/>
+    <mergeCell ref="A6:U6"/>
+    <mergeCell ref="C52:U52"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:P15"/>
+    <mergeCell ref="Q15:U15"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:C22"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="C54:U54"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="A16:C17"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:C26"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:C24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="C58:U58"/>
+    <mergeCell ref="O39:O40"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="L8:U8"/>
     <mergeCell ref="L10:U10"/>
@@ -3291,74 +3172,22 @@
     <mergeCell ref="Q31:U32"/>
     <mergeCell ref="Q33:U34"/>
     <mergeCell ref="D29:G30"/>
-    <mergeCell ref="C60:U60"/>
-    <mergeCell ref="A6:U6"/>
-    <mergeCell ref="C52:U52"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:P15"/>
-    <mergeCell ref="Q15:U15"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:C22"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="C54:U54"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="A16:C17"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:C26"/>
-    <mergeCell ref="P21:P22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:C24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="C58:U58"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="P39:P40"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D21:G22"/>
-    <mergeCell ref="I21:N22"/>
-    <mergeCell ref="D23:G24"/>
-    <mergeCell ref="I23:N24"/>
-    <mergeCell ref="D25:G26"/>
-    <mergeCell ref="I25:N26"/>
-    <mergeCell ref="D27:G28"/>
-    <mergeCell ref="I27:N28"/>
-    <mergeCell ref="D16:G17"/>
-    <mergeCell ref="I16:N17"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:C32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="O29:O30"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="I29:N30"/>
-    <mergeCell ref="D31:G32"/>
-    <mergeCell ref="B29:C30"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="K3:M3"/>
-    <mergeCell ref="I31:N32"/>
-    <mergeCell ref="D33:G34"/>
-    <mergeCell ref="I33:N34"/>
-    <mergeCell ref="D35:G36"/>
-    <mergeCell ref="I35:N36"/>
-    <mergeCell ref="D37:G38"/>
-    <mergeCell ref="I37:N38"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="P33:P34"/>
-    <mergeCell ref="O27:O28"/>
-    <mergeCell ref="P27:P28"/>
-    <mergeCell ref="P37:P38"/>
-    <mergeCell ref="P35:P36"/>
-    <mergeCell ref="O33:O34"/>
-    <mergeCell ref="O35:O36"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="C56:U56"/>
+    <mergeCell ref="I42:P43"/>
+    <mergeCell ref="Q42:U43"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:C40"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:C36"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="Q35:U36"/>
+    <mergeCell ref="Q37:U38"/>
+    <mergeCell ref="Q39:U40"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="I39:N40"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3371,290 +3200,4 @@
     <ignoredError sqref="B32:C32 B31:C31 B34:C34 B33:C33 B36:C36 B35:C35 B38:C38 B37:C37 B40:C40 B39:C39 A40 A38 A36 A34 A30 A28 A32 A26 A21:A25 A27 A33 A29 A31 A35 A37 A39" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101004F04D70F81502745934EEFA6067428B0" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="e4b1285e22ba7abc44906dbb08eaf091">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2bc05441-ecb8-41d0-9872-2862fef3ebb0" xmlns:ns3="263dbbe5-076b-4606-a03b-9598f5f2f35a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f178929248ea575f95a3ed45aedf7b59" ns2:_="" ns3:_="">
-    <xsd:import namespace="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
-    <xsd:import namespace="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:Owner" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2bc05441-ecb8-41d0-9872-2862fef3ebb0" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="Owner" ma:index="8" nillable="true" ma:displayName="所有者" ma:internalName="Owner">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:User">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="0347f584-7be2-4218-8e94-402d99aedf0b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="263dbbe5-076b-4606-a03b-9598f5f2f35a" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="15" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{4cf81088-27f6-4285-b4a6-5b8a1b98758a}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="263dbbe5-076b-4606-a03b-9598f5f2f35a">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Owner xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80FAA9F3-FF3E-46D1-8B5E-847A0A028318}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
-    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AFE2099-AC38-4CEA-BF2F-903A89332FBE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{219D3A97-D4F9-48B1-92B9-1B14DBC52F43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <ds:schemaRef ds:uri="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>